--- a/templates/TATA Capital/TATA_Stockyard_Agency_Template_2026-27.xlsx
+++ b/templates/TATA Capital/TATA_Stockyard_Agency_Template_2026-27.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachit Goyal\Downloads\audit-report-generator\templates\TATA Capital\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachit Goyal\Downloads\audit-automation-final\templates\TATA Capital\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE508CE-2AA3-44C2-98A8-F0FA43893524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{019D89BE-707F-4A75-8E47-DC148871FDCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1500" yWindow="1500" windowWidth="13152" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Checklist" sheetId="8" r:id="rId1"/>
@@ -36,8 +36,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -627,11 +625,11 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -957,6 +955,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A2:J42"/>
   <sheetFormatPr defaultColWidth="46" defaultRowHeight="12" x14ac:dyDescent="0.3"/>
   <cols>
@@ -974,7 +975,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="39"/>
+      <c r="B2" s="38"/>
       <c r="C2" s="5" t="s">
         <v>15</v>
       </c>
@@ -986,7 +987,7 @@
       <c r="G2" s="9"/>
     </row>
     <row r="3" spans="1:10" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="39"/>
+      <c r="B3" s="38"/>
       <c r="C3" s="5" t="s">
         <v>16</v>
       </c>
@@ -998,7 +999,7 @@
       <c r="G3" s="9"/>
     </row>
     <row r="4" spans="1:10" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="39"/>
+      <c r="B4" s="38"/>
       <c r="C4" s="5" t="s">
         <v>17</v>
       </c>
@@ -1010,7 +1011,7 @@
       <c r="G4" s="9"/>
     </row>
     <row r="5" spans="1:10" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="39"/>
+      <c r="B5" s="38"/>
       <c r="C5" s="5" t="s">
         <v>70</v>
       </c>
@@ -1941,12 +1942,15 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="45" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="45" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:E15"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2077,12 +2081,12 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="38"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="38"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
       <c r="E7" s="19" t="str">
         <f>IF(E6&gt;=0.8,"A",IF(E6&gt;=0.7,"B",IF(E6&gt;=0.6,"C",IF(E6&gt;=0.5,"D","E"))))</f>
         <v>A</v>
@@ -2166,7 +2170,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="91" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="91" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2317,12 +2321,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="0115396f-2e4a-4d2a-ba9c-df4d17cb71a2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2565,17 +2568,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="0115396f-2e4a-4d2a-ba9c-df4d17cb71a2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A441EEC-55BA-46EA-90EF-FC0D7755347D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2F59799-9B83-49D0-A943-0DC9FFAB44BC}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="0115396f-2e4a-4d2a-ba9c-df4d17cb71a2"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="2bc29a05-2ca3-4765-9547-41c11361a102"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2600,18 +2613,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2F59799-9B83-49D0-A943-0DC9FFAB44BC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A441EEC-55BA-46EA-90EF-FC0D7755347D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="0115396f-2e4a-4d2a-ba9c-df4d17cb71a2"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="2bc29a05-2ca3-4765-9547-41c11361a102"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>